--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דניאלה גולדפיין – Like a Swing</v>
+        <v>אסתר שמיר ויהל דורון – בצד השני של הפחד</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c%d7%94-%d7%92%d7%95%d7%9c%d7%93%d7%a4%d7%99%d7%99%d7%9f-like-a-swing/</v>
+        <v>https://yosmusic.com/%d7%90%d7%a1%d7%aa%d7%a8-%d7%a9%d7%9e%d7%99%d7%a8-%d7%95%d7%99%d7%94%d7%9c-%d7%93%d7%95%d7%a8%d7%95%d7%9f-%d7%91%d7%a6%d7%93-%d7%94%d7%a9%d7%a0%d7%99-%d7%a9%d7%9c-%d7%94%d7%a4%d7%97%d7%93/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “Like a Swing” של דניאלה גולדפיין נוגע ומגיע מתוך הפשטות שלו. אין כאן ניסיון להרשים בהפקה גדולה, מהלכים דרמטיים או כתיבה מתוחכמת מדי, אלא יצירה קטנה, אינטימית וכמעט חשופה, שנשמעת כמו מכתב אישי שהולחן ברגע שקט באמצע הלילה. הרעיון</v>
+        <v>שיתוף הפעולה בין אסתר שמיר ליהל דורון ב״בצד השני של הפחד״ הוא לא רק דואט מוזיקלי  אלא מפגש בין שתי תפיסות של רגש, כתיבה ונחמה במוזיקה הישראלית. מצד אחד קול שנושא איתו היסטוריה תרבותית שלמה, ומצד שני יוצר עכשווי שמביא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דניאלה גולדפיין – Like a Swing</v>
+        <v>אסתר שמיר ויהל דורון – בצד השני של הפחד</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אסתר שמיר ויהל דורון – בצד השני של הפחד</v>
+        <v>אביגייל רוז – רגעים של שפיות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a1%d7%aa%d7%a8-%d7%a9%d7%9e%d7%99%d7%a8-%d7%95%d7%99%d7%94%d7%9c-%d7%93%d7%95%d7%a8%d7%95%d7%9f-%d7%91%d7%a6%d7%93-%d7%94%d7%a9%d7%a0%d7%99-%d7%a9%d7%9c-%d7%94%d7%a4%d7%97%d7%93/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%99%d7%92%d7%99%d7%99%d7%9c-%d7%a8%d7%95%d7%96-%d7%a8%d7%92%d7%a2%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a9%d7%a4%d7%99%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>שיתוף הפעולה בין אסתר שמיר ליהל דורון ב״בצד השני של הפחד״ הוא לא רק דואט מוזיקלי  אלא מפגש בין שתי תפיסות של רגש, כתיבה ונחמה במוזיקה הישראלית. מצד אחד קול שנושא איתו היסטוריה תרבותית שלמה, ומצד שני יוצר עכשווי שמביא</v>
+        <v>אביגייל רוז בונה ב״רגעים של שפיות״ בלדה שנעה בין אינטימיות כמעט לוחשת לבין התפרצות רגשית דרמטית. הטקסט, ההלחנה והעיבוד עובדים יחד כדי לתאר תהליך נפשי: ניסיון להחזיק את החיים בשליטה – ואז רגע של קריסה, או אולי שחרור. השיר נפתח</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אסתר שמיר ויהל דורון – בצד השני של הפחד</v>
+        <v>אביגייל רוז – רגעים של שפיות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביגייל רוז – רגעים של שפיות</v>
+        <v>נתלי – באמא שך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%99%d7%92%d7%99%d7%99%d7%9c-%d7%a8%d7%95%d7%96-%d7%a8%d7%92%d7%a2%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a9%d7%a4%d7%99%d7%95%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%9c%d7%99-%d7%91%d7%90%d7%9e%d7%90-%d7%a9%d7%9a/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אביגייל רוז בונה ב״רגעים של שפיות״ בלדה שנעה בין אינטימיות כמעט לוחשת לבין התפרצות רגשית דרמטית. הטקסט, ההלחנה והעיבוד עובדים יחד כדי לתאר תהליך נפשי: ניסיון להחזיק את החיים בשליטה – ואז רגע של קריסה, או אולי שחרור. השיר נפתח</v>
+        <v>נתלי צפר ב״באמא שך״ יוצרת שיר פרידה כועס, עייף ופגיע בו־זמנית – כזה שמסתיר כאב עמוק מאחורי שפה יומיומית, כמעט רחובית. הכוח של השיר נמצא בדיוק בפער הזה: בין הקצב הריקודי והעיבוד הלטיני־ים־תיכוני לבין הטקסט שמתאר מערכת יחסים רעילה, מתישה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אביגייל רוז – רגעים של שפיות</v>
+        <v>נתלי – באמא שך</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נתלי – באמא שך</v>
+        <v>כנסיית השכל ואיתן רייטר – השיר מהגן</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%9c%d7%99-%d7%91%d7%90%d7%9e%d7%90-%d7%a9%d7%9a/</v>
+        <v>https://yosmusic.com/%d7%9b%d7%a0%d7%a1%d7%99%d7%99%d7%aa-%d7%94%d7%a9%d7%9b%d7%9c-%d7%95%d7%90%d7%99%d7%aa%d7%9f-%d7%a8%d7%99%d7%99%d7%98%d7%a8-%d7%94%d7%a9%d7%99%d7%a8-%d7%9e%d7%94%d7%92%d7%9f/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>נתלי צפר ב״באמא שך״ יוצרת שיר פרידה כועס, עייף ופגיע בו־זמנית – כזה שמסתיר כאב עמוק מאחורי שפה יומיומית, כמעט רחובית. הכוח של השיר נמצא בדיוק בפער הזה: בין הקצב הריקודי והעיבוד הלטיני־ים־תיכוני לבין הטקסט שמתאר מערכת יחסים רעילה, מתישה</v>
+        <v>הרמיקס ל־“שיר מהגן” מצליח לקחת את הרגש הנוסטלגי והחשוף של כנסיית השכל ולהעביר אותו דרך פילטר אלקטרוני מהפנט של איתן רייטר – בלי לאבד את הלב של השיר. הטקסט  נשען על זיכרון חלקי, כמעט שבור:הדובר לא זוכר “את השיר מהגן”,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נתלי – באמא שך</v>
+        <v>כנסיית השכל ואיתן רייטר – השיר מהגן</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>כנסיית השכל ואיתן רייטר – השיר מהגן</v>
+        <v>נרקיס – שעת רצון</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9b%d7%a0%d7%a1%d7%99%d7%99%d7%aa-%d7%94%d7%a9%d7%9b%d7%9c-%d7%95%d7%90%d7%99%d7%aa%d7%9f-%d7%a8%d7%99%d7%99%d7%98%d7%a8-%d7%94%d7%a9%d7%99%d7%a8-%d7%9e%d7%94%d7%92%d7%9f/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%a8%d7%a7%d7%99%d7%a1-%d7%a9%d7%a2%d7%aa-%d7%a8%d7%a6%d7%95%d7%9f/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הרמיקס ל־“שיר מהגן” מצליח לקחת את הרגש הנוסטלגי והחשוף של כנסיית השכל ולהעביר אותו דרך פילטר אלקטרוני מהפנט של איתן רייטר – בלי לאבד את הלב של השיר. הטקסט  נשען על זיכרון חלקי, כמעט שבור:הדובר לא זוכר “את השיר מהגן”,</v>
+        <v>"שעת רצון” של נרקיס מנסה להיות הרבה יותר משיר אהבה: הוא מבקש לתפקד כמעט כתפילה פופולרית־רוחנית. זה שיר על תיקון, אמונה, ריפוי זוגי ופנימי, האפשרות “להחזיר אור” בתוך מציאות שבורה. אבל בדיוק בנקודה הזאת נמצאת גם החולשה הגדולה שלו. יש</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>כנסיית השכל ואיתן רייטר – השיר מהגן</v>
+        <v>נרקיס – שעת רצון</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נרקיס – שעת רצון</v>
+        <v>דניאל וייס – מכור</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%a8%d7%a7%d7%99%d7%a1-%d7%a9%d7%a2%d7%aa-%d7%a8%d7%a6%d7%95%d7%9f/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c-%d7%95%d7%99%d7%99%d7%a1-%d7%9e%d7%9b%d7%95%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"שעת רצון” של נרקיס מנסה להיות הרבה יותר משיר אהבה: הוא מבקש לתפקד כמעט כתפילה פופולרית־רוחנית. זה שיר על תיקון, אמונה, ריפוי זוגי ופנימי, האפשרות “להחזיר אור” בתוך מציאות שבורה. אבל בדיוק בנקודה הזאת נמצאת גם החולשה הגדולה שלו. יש</v>
+        <v>דניאל וייס שר על החיים בתוך תרבות של עודף – עוד גירויים, עוד רעש, עוד בריחה.זה שיר שלא מדבר על התמכרות קיצונית, אלא על ההתמכרויות המתפקדות, היומיומיות, שכבר נטמעו בתוך שגרת החיים המודרנית עד שהן נראות נורמליות לגמרי. הוא לא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נרקיס – שעת רצון</v>
+        <v>דניאל וייס – מכור</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דניאל וייס – מכור</v>
+        <v>שלמה בר מארח את אהוד בנאי – צור משלו אכלנו</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c-%d7%95%d7%99%d7%99%d7%a1-%d7%9e%d7%9b%d7%95%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%91%d7%a8-%d7%9e%d7%90%d7%a8%d7%97-%d7%90%d7%aa-%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%a6%d7%95%d7%a8-%d7%9e%d7%a9%d7%9c%d7%95-%d7%90%d7%9b%d7%9c%d7%a0%d7%95/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-27</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>דניאל וייס שר על החיים בתוך תרבות של עודף – עוד גירויים, עוד רעש, עוד בריחה.זה שיר שלא מדבר על התמכרות קיצונית, אלא על ההתמכרויות המתפקדות, היומיומיות, שכבר נטמעו בתוך שגרת החיים המודרנית עד שהן נראות נורמליות לגמרי. הוא לא</v>
+        <v>הגרסה החדשה של "צור משלו אכלנו” של שלמה בר יחד עם אהוד בנאי היא הרבה מעבר לעיבוד מחודש לפיוט מוכר. זהו מפגש בין שתי תפיסות רוחניות־מוזיקליות של המוזיקה הישראלית- הטקסיות השבטית־מרוקאית של שלמה בר מול רוח הנדודים העירוניים־המדבריים של אהוד</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דניאל וייס – מכור</v>
+        <v>שלמה בר מארח את אהוד בנאי – צור משלו אכלנו</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-05-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלמה בר מארח את אהוד בנאי – צור משלו אכלנו</v>
+        <v>בר צברי – ככה באמת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%91%d7%a8-%d7%9e%d7%90%d7%a8%d7%97-%d7%90%d7%aa-%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%a6%d7%95%d7%a8-%d7%9e%d7%a9%d7%9c%d7%95-%d7%90%d7%9b%d7%9c%d7%a0%d7%95/</v>
+        <v>https://yosmusic.com/%d7%91%d7%a8-%d7%a6%d7%91%d7%a8%d7%99-%d7%9b%d7%9b%d7%94-%d7%91%d7%90%d7%9e%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הגרסה החדשה של "צור משלו אכלנו” של שלמה בר יחד עם אהוד בנאי היא הרבה מעבר לעיבוד מחודש לפיוט מוכר. זהו מפגש בין שתי תפיסות רוחניות־מוזיקליות של המוזיקה הישראלית- הטקסיות השבטית־מרוקאית של שלמה בר מול רוח הנדודים העירוניים־המדבריים של אהוד</v>
+        <v>בר צברי שר שיר אהבה שמצליח לגעת דווקא בגלל הפשטות שלו. הוא לא מנסה להיות פיוטי מדי, מתוחכם מדי או דרמטי מדי  אלא נשען על דיבור ישיר, כמעט יומיומי, שמבקש לומר דבר אחד פשוט: אהבה אמיתית נבנית מהחיים עצמם, וזה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלמה בר מארח את אהוד בנאי – צור משלו אכלנו</v>
+        <v>בר צברי – ככה באמת</v>
       </c>
     </row>
   </sheetData>
